--- a/LLM_evaluate/master_comparison.xlsx
+++ b/LLM_evaluate/master_comparison.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="E5" s="5" t="n">
@@ -580,25 +580,25 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.045</v>
+        <v/>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.207</v>
+        <v/>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.046</v>
+        <v/>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.151</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -614,7 +614,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -623,16 +623,16 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.047</v>
+        <v/>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.189</v>
+        <v/>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.044</v>
+        <v/>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.147</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -648,31 +648,31 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.036</v>
+        <v>0.033</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.112</v>
+        <v>0.196</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.038</v>
+        <v>0.032</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.161</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-7B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -682,31 +682,31 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.003</v>
+        <v>0.045</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.111</v>
+        <v>0.207</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.004</v>
+        <v>0.046</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.082</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-7B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.037</v>
+        <v>0.045</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.253</v>
+        <v>0.207</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.031</v>
+        <v>0.046</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.162</v>
+        <v>0.151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-7B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -755,26 +755,26 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.062</v>
+        <v>0.037</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.396</v>
+        <v>0.179</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.057</v>
+        <v>0.03</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.282</v>
+        <v>0.132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-7B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -784,41 +784,41 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.053</v>
+        <v>0.047</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.293</v>
+        <v>0.189</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.052</v>
+        <v>0.044</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.172</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -827,95 +827,95 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.022</v>
+        <v>0.047</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.577</v>
+        <v>0.189</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.031</v>
+        <v>0.044</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.14</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.119</v>
+        <v>0.036</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.383</v>
+        <v>0.113</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.094</v>
+        <v>0.038</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.271</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.11</v>
+        <v>0.036</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.336</v>
+        <v>0.112</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.09</v>
+        <v>0.038</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.231</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Llama-3.1-70B</t>
+          <t>Llama-3.1-8B</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -929,27 +929,27 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.058</v>
+        <v>0.036</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.112</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.066</v>
+        <v>0.038</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.161</v>
+        <v>0.08699999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-72B</t>
+          <t>Qwen-2.5-7B</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -959,70 +959,70 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>ade</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.264</v>
+        <v>0.003</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.677</v>
+        <v>0.111</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.416</v>
+        <v>0.004</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.174</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-72B</t>
+          <t>Qwen-2.5-7B</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>abcde</t>
+          <t>abde</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.23</v>
+        <v>0.003</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.447</v>
+        <v>0.111</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.249</v>
+        <v>0.004</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.254</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Qwen-2.5-72B</t>
+          <t>Qwen-2.5-7B</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1031,49 +1031,1137 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.209</v>
+        <v>0.003</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.403</v>
+        <v>0.111</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.206</v>
+        <v>0.004</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.241</v>
+        <v>0.082</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.162</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.282</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.282</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-7B</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.111</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.119</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.271</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.309</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H36" s="5" t="n">
+        <v>0.231</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.231</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.628</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.303</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Llama-3.1-70B</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.161</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t>Qwen-2.5-72B</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0.172</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.174</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.174</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.251</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.254</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0.447</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.254</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>abcde</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.206</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.241</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>ade</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.275</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>abde</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.181</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Qwen-2.5-72B</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>abcde</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E52" s="5" t="n">
         <v>0.334</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F52" s="5" t="n">
         <v>0.509</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G52" s="5" t="n">
         <v>0.409</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H52" s="5" t="n">
         <v>0.181</v>
       </c>
     </row>
@@ -1082,7 +2170,7 @@
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E20">
+  <conditionalFormatting sqref="E5:E52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1094,7 +2182,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F20">
+  <conditionalFormatting sqref="F5:F52">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1106,7 +2194,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G20">
+  <conditionalFormatting sqref="G5:G52">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1118,7 +2206,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H20">
+  <conditionalFormatting sqref="H5:H52">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
